--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.04486</v>
+        <v>17.1646</v>
       </c>
       <c r="D2" t="n">
-        <v>17.01976</v>
+        <v>16.91721</v>
       </c>
       <c r="E2" t="n">
-        <v>17.40028</v>
+        <v>16.98568</v>
       </c>
       <c r="F2" t="n">
-        <v>42.41268</v>
+        <v>42.9256</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05247</v>
+        <v>0.05075</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85029</v>
+        <v>1.89305</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.83472</v>
+        <v>16.85523</v>
       </c>
       <c r="D3" t="n">
-        <v>16.89687</v>
+        <v>16.78797</v>
       </c>
       <c r="E3" t="n">
-        <v>17.02098</v>
+        <v>16.83251</v>
       </c>
       <c r="F3" t="n">
-        <v>41.64834</v>
+        <v>43.22242</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05157</v>
+        <v>0.05184</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83695</v>
+        <v>1.89031</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.87175</v>
+        <v>17.02335</v>
       </c>
       <c r="D4" t="n">
-        <v>16.90788</v>
+        <v>16.55995</v>
       </c>
       <c r="E4" t="n">
-        <v>17.06451</v>
+        <v>16.80085</v>
       </c>
       <c r="F4" t="n">
-        <v>43.25039</v>
+        <v>42.63626</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0501</v>
+        <v>0.05141</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8501</v>
+        <v>1.85555</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.8697</v>
+        <v>17.25436</v>
       </c>
       <c r="D5" t="n">
-        <v>16.65625</v>
+        <v>16.50023</v>
       </c>
       <c r="E5" t="n">
-        <v>17.02451</v>
+        <v>16.82129</v>
       </c>
       <c r="F5" t="n">
-        <v>42.90185</v>
+        <v>43.42671</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05206</v>
+        <v>0.05155</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82102</v>
+        <v>1.83987</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.38453</v>
+        <v>17.09014</v>
       </c>
       <c r="D6" t="n">
-        <v>16.5694</v>
+        <v>16.53483</v>
       </c>
       <c r="E6" t="n">
-        <v>17.20984</v>
+        <v>16.74561</v>
       </c>
       <c r="F6" t="n">
-        <v>42.82662</v>
+        <v>42.96112</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05074</v>
+        <v>0.05111</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81731</v>
+        <v>1.80111</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.79445</v>
+        <v>17.07088</v>
       </c>
       <c r="D7" t="n">
-        <v>16.81285</v>
+        <v>16.7721</v>
       </c>
       <c r="E7" t="n">
-        <v>16.65269</v>
+        <v>17.00086</v>
       </c>
       <c r="F7" t="n">
-        <v>43.54127</v>
+        <v>42.73811</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05156</v>
+        <v>0.05208</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84947</v>
+        <v>1.87001</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.97904</v>
+        <v>17.2318</v>
       </c>
       <c r="D8" t="n">
-        <v>16.70554</v>
+        <v>16.73291</v>
       </c>
       <c r="E8" t="n">
-        <v>16.96537</v>
+        <v>17.11347</v>
       </c>
       <c r="F8" t="n">
-        <v>44.08583</v>
+        <v>43.58016</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0511</v>
+        <v>0.05112</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80593</v>
+        <v>1.83359</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.89524</v>
+        <v>17.24643</v>
       </c>
       <c r="D9" t="n">
-        <v>16.65912</v>
+        <v>16.49636</v>
       </c>
       <c r="E9" t="n">
-        <v>17.10599</v>
+        <v>16.92406</v>
       </c>
       <c r="F9" t="n">
-        <v>43.50412</v>
+        <v>42.85882</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05188</v>
+        <v>0.05179</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82061</v>
+        <v>1.84803</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.99861</v>
+        <v>17.03846</v>
       </c>
       <c r="D10" t="n">
-        <v>16.68052</v>
+        <v>16.52508</v>
       </c>
       <c r="E10" t="n">
-        <v>16.57846</v>
+        <v>16.82917</v>
       </c>
       <c r="F10" t="n">
-        <v>43.64364</v>
+        <v>42.26351</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05085</v>
+        <v>0.05114</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84981</v>
+        <v>1.85734</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.75824</v>
+        <v>17.40317</v>
       </c>
       <c r="D12" t="n">
-        <v>16.66625</v>
+        <v>16.75628</v>
       </c>
       <c r="E12" t="n">
-        <v>16.77042</v>
+        <v>16.79106</v>
       </c>
       <c r="F12" t="n">
-        <v>42.80773</v>
+        <v>42.21568</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05068</v>
+        <v>0.05127</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81426</v>
+        <v>1.82709</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.76294</v>
+        <v>17.03924</v>
       </c>
       <c r="D13" t="n">
-        <v>16.7648</v>
+        <v>16.55336</v>
       </c>
       <c r="E13" t="n">
-        <v>16.77941</v>
+        <v>16.82077</v>
       </c>
       <c r="F13" t="n">
-        <v>43.17283</v>
+        <v>42.73829</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0511</v>
+        <v>0.05019</v>
       </c>
       <c r="H13" t="n">
-        <v>1.86959</v>
+        <v>1.83287</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.62335</v>
+        <v>16.89217</v>
       </c>
       <c r="D14" t="n">
-        <v>16.82755</v>
+        <v>16.87855</v>
       </c>
       <c r="E14" t="n">
-        <v>16.77581</v>
+        <v>16.88764</v>
       </c>
       <c r="F14" t="n">
-        <v>42.86929</v>
+        <v>42.97461</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05118</v>
+        <v>0.05088</v>
       </c>
       <c r="H14" t="n">
-        <v>1.84069</v>
+        <v>1.85103</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.14682</v>
+        <v>16.93558</v>
       </c>
       <c r="D15" t="n">
-        <v>16.26198</v>
+        <v>16.56021</v>
       </c>
       <c r="E15" t="n">
-        <v>16.93828</v>
+        <v>16.71897</v>
       </c>
       <c r="F15" t="n">
-        <v>43.96724</v>
+        <v>43.04365</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05231</v>
+        <v>0.05088</v>
       </c>
       <c r="H15" t="n">
-        <v>1.88773</v>
+        <v>1.82152</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.17489</v>
+        <v>17.13189</v>
       </c>
       <c r="D16" t="n">
-        <v>16.74778</v>
+        <v>16.89385</v>
       </c>
       <c r="E16" t="n">
-        <v>16.54372</v>
+        <v>17.07278</v>
       </c>
       <c r="F16" t="n">
-        <v>42.5722</v>
+        <v>43.70215</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05069</v>
+        <v>0.05112</v>
       </c>
       <c r="H16" t="n">
-        <v>1.85304</v>
+        <v>1.84778</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.71396</v>
+        <v>17.02125</v>
       </c>
       <c r="D17" t="n">
-        <v>16.57119</v>
+        <v>16.74296</v>
       </c>
       <c r="E17" t="n">
-        <v>16.90052</v>
+        <v>16.90829</v>
       </c>
       <c r="F17" t="n">
-        <v>42.09856</v>
+        <v>43.79516</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05049</v>
+        <v>0.05194</v>
       </c>
       <c r="H17" t="n">
-        <v>1.84859</v>
+        <v>1.8831</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.951</v>
+        <v>16.95774</v>
       </c>
       <c r="D18" t="n">
-        <v>16.93991</v>
+        <v>16.61102</v>
       </c>
       <c r="E18" t="n">
-        <v>16.41037</v>
+        <v>16.94018</v>
       </c>
       <c r="F18" t="n">
-        <v>42.93704</v>
+        <v>43.62688</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05063</v>
+        <v>0.05118</v>
       </c>
       <c r="H18" t="n">
-        <v>1.84246</v>
+        <v>1.83825</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.105</v>
+        <v>16.77425</v>
       </c>
       <c r="D19" t="n">
-        <v>16.70301</v>
+        <v>16.74253</v>
       </c>
       <c r="E19" t="n">
-        <v>16.8909</v>
+        <v>16.77362</v>
       </c>
       <c r="F19" t="n">
-        <v>43.90265</v>
+        <v>42.54492</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05128</v>
+        <v>0.05022</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84756</v>
+        <v>1.80513</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.02179</v>
+        <v>17.02459</v>
       </c>
       <c r="D20" t="n">
-        <v>16.73863</v>
+        <v>16.79668</v>
       </c>
       <c r="E20" t="n">
-        <v>16.89675</v>
+        <v>16.88896</v>
       </c>
       <c r="F20" t="n">
-        <v>43.18451</v>
+        <v>43.61682</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05082</v>
+        <v>0.05112</v>
       </c>
       <c r="H20" t="n">
-        <v>1.83877</v>
+        <v>1.8034</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.85959</v>
+        <v>15.61343</v>
       </c>
       <c r="D22" t="n">
-        <v>16.0985</v>
+        <v>15.48036</v>
       </c>
       <c r="E22" t="n">
-        <v>15.66015</v>
+        <v>15.60278</v>
       </c>
       <c r="F22" t="n">
-        <v>253.11037</v>
+        <v>256.58146</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.06792</v>
+        <v>15.78715</v>
       </c>
       <c r="D23" t="n">
-        <v>16.01819</v>
+        <v>15.66989</v>
       </c>
       <c r="E23" t="n">
-        <v>15.724</v>
+        <v>15.69749</v>
       </c>
       <c r="F23" t="n">
-        <v>253.37599</v>
+        <v>258.55916</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.12381</v>
+        <v>16.06855</v>
       </c>
       <c r="D24" t="n">
-        <v>15.67432</v>
+        <v>15.48346</v>
       </c>
       <c r="E24" t="n">
-        <v>15.72229</v>
+        <v>15.83826</v>
       </c>
       <c r="F24" t="n">
-        <v>257.55763</v>
+        <v>259.71324</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.98397</v>
+        <v>15.64993</v>
       </c>
       <c r="D25" t="n">
-        <v>16.11904</v>
+        <v>15.5486</v>
       </c>
       <c r="E25" t="n">
-        <v>15.68971</v>
+        <v>15.61857</v>
       </c>
       <c r="F25" t="n">
-        <v>262.26592</v>
+        <v>254.50576</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.72391</v>
+        <v>15.94408</v>
       </c>
       <c r="D26" t="n">
-        <v>15.92906</v>
+        <v>15.60205</v>
       </c>
       <c r="E26" t="n">
-        <v>16.02044</v>
+        <v>15.86474</v>
       </c>
       <c r="F26" t="n">
-        <v>260.74266</v>
+        <v>255.13072</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.11188</v>
+        <v>15.99832</v>
       </c>
       <c r="D27" t="n">
-        <v>15.80331</v>
+        <v>15.6343</v>
       </c>
       <c r="E27" t="n">
-        <v>15.92626</v>
+        <v>15.85383</v>
       </c>
       <c r="F27" t="n">
-        <v>255.39429</v>
+        <v>253.97785</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.04996</v>
+        <v>16.04822</v>
       </c>
       <c r="D28" t="n">
-        <v>15.85178</v>
+        <v>15.86929</v>
       </c>
       <c r="E28" t="n">
-        <v>15.62478</v>
+        <v>16.04481</v>
       </c>
       <c r="F28" t="n">
-        <v>261.96798</v>
+        <v>255.85324</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.51517</v>
+        <v>15.86409</v>
       </c>
       <c r="D29" t="n">
-        <v>15.66565</v>
+        <v>15.54036</v>
       </c>
       <c r="E29" t="n">
-        <v>15.56841</v>
+        <v>15.78025</v>
       </c>
       <c r="F29" t="n">
-        <v>256.03746</v>
+        <v>253.91533</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.64603</v>
+        <v>16.06442</v>
       </c>
       <c r="D30" t="n">
-        <v>15.41298</v>
+        <v>15.73352</v>
       </c>
       <c r="E30" t="n">
-        <v>16.09896</v>
+        <v>15.73623</v>
       </c>
       <c r="F30" t="n">
-        <v>255.83057</v>
+        <v>266.07741</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.95613</v>
+        <v>17.2184</v>
       </c>
       <c r="D32" t="n">
-        <v>16.4052</v>
+        <v>16.37561</v>
       </c>
       <c r="E32" t="n">
-        <v>16.4851</v>
+        <v>16.56326</v>
       </c>
       <c r="F32" t="n">
-        <v>21.67295</v>
+        <v>21.96757</v>
       </c>
       <c r="G32" t="n">
-        <v>34.65588</v>
+        <v>34.35323</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.67473</v>
+        <v>16.90998</v>
       </c>
       <c r="D33" t="n">
-        <v>16.46238</v>
+        <v>16.15558</v>
       </c>
       <c r="E33" t="n">
-        <v>16.28177</v>
+        <v>16.3579</v>
       </c>
       <c r="F33" t="n">
-        <v>22.46586</v>
+        <v>22.31779</v>
       </c>
       <c r="G33" t="n">
-        <v>35.02116</v>
+        <v>35.05984</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.39809</v>
+        <v>16.72268</v>
       </c>
       <c r="D34" t="n">
-        <v>16.04831</v>
+        <v>16.4692</v>
       </c>
       <c r="E34" t="n">
-        <v>16.72151</v>
+        <v>16.47227</v>
       </c>
       <c r="F34" t="n">
-        <v>22.42231</v>
+        <v>22.59364</v>
       </c>
       <c r="G34" t="n">
-        <v>34.16857</v>
+        <v>34.5958</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.95829</v>
+        <v>16.86249</v>
       </c>
       <c r="D35" t="n">
-        <v>15.95444</v>
+        <v>16.12035</v>
       </c>
       <c r="E35" t="n">
-        <v>16.59121</v>
+        <v>16.791</v>
       </c>
       <c r="F35" t="n">
-        <v>22.29563</v>
+        <v>22.05158</v>
       </c>
       <c r="G35" t="n">
-        <v>34.70981</v>
+        <v>34.81508</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17.10671</v>
+        <v>17.06148</v>
       </c>
       <c r="D36" t="n">
-        <v>16.47471</v>
+        <v>16.11757</v>
       </c>
       <c r="E36" t="n">
-        <v>16.61075</v>
+        <v>16.57085</v>
       </c>
       <c r="F36" t="n">
-        <v>22.21297</v>
+        <v>22.35565</v>
       </c>
       <c r="G36" t="n">
-        <v>34.30808</v>
+        <v>34.43487</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.94789</v>
+        <v>16.6752</v>
       </c>
       <c r="D37" t="n">
-        <v>16.44954</v>
+        <v>16.09207</v>
       </c>
       <c r="E37" t="n">
-        <v>16.44244</v>
+        <v>16.4917</v>
       </c>
       <c r="F37" t="n">
-        <v>21.52439</v>
+        <v>22.1231</v>
       </c>
       <c r="G37" t="n">
-        <v>34.502</v>
+        <v>34.35954</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>17.02479</v>
+        <v>16.77917</v>
       </c>
       <c r="D38" t="n">
-        <v>15.93671</v>
+        <v>16.36546</v>
       </c>
       <c r="E38" t="n">
-        <v>16.91162</v>
+        <v>16.55657</v>
       </c>
       <c r="F38" t="n">
-        <v>22.41363</v>
+        <v>22.02203</v>
       </c>
       <c r="G38" t="n">
-        <v>34.56516</v>
+        <v>34.56387</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.81521</v>
+        <v>16.86479</v>
       </c>
       <c r="D39" t="n">
-        <v>15.88075</v>
+        <v>16.46953</v>
       </c>
       <c r="E39" t="n">
-        <v>16.38021</v>
+        <v>16.57866</v>
       </c>
       <c r="F39" t="n">
-        <v>21.975</v>
+        <v>22.05907</v>
       </c>
       <c r="G39" t="n">
-        <v>34.60376</v>
+        <v>35.7515</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.85654</v>
+        <v>16.75488</v>
       </c>
       <c r="D40" t="n">
-        <v>16.33938</v>
+        <v>16.40487</v>
       </c>
       <c r="E40" t="n">
-        <v>16.83307</v>
+        <v>16.5186</v>
       </c>
       <c r="F40" t="n">
-        <v>21.72594</v>
+        <v>21.96183</v>
       </c>
       <c r="G40" t="n">
-        <v>35.17207</v>
+        <v>34.74955</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.77394</v>
+        <v>17.06562</v>
       </c>
       <c r="D42" t="n">
-        <v>16.13518</v>
+        <v>16.02186</v>
       </c>
       <c r="E42" t="n">
-        <v>16.60462</v>
+        <v>16.45215</v>
       </c>
       <c r="F42" t="n">
-        <v>21.81228</v>
+        <v>21.84038</v>
       </c>
       <c r="G42" t="n">
-        <v>34.39849</v>
+        <v>34.05061</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.85686</v>
+        <v>16.89847</v>
       </c>
       <c r="D43" t="n">
-        <v>16.3016</v>
+        <v>16.35699</v>
       </c>
       <c r="E43" t="n">
-        <v>16.67838</v>
+        <v>16.54006</v>
       </c>
       <c r="F43" t="n">
-        <v>22.46373</v>
+        <v>21.99814</v>
       </c>
       <c r="G43" t="n">
-        <v>34.8299</v>
+        <v>34.16242</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.89942</v>
+        <v>16.73218</v>
       </c>
       <c r="D44" t="n">
-        <v>16.15814</v>
+        <v>16.6707</v>
       </c>
       <c r="E44" t="n">
-        <v>16.60165</v>
+        <v>16.68804</v>
       </c>
       <c r="F44" t="n">
-        <v>21.64074</v>
+        <v>21.98898</v>
       </c>
       <c r="G44" t="n">
-        <v>34.29774</v>
+        <v>34.44335</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17.10634</v>
+        <v>16.74903</v>
       </c>
       <c r="D45" t="n">
-        <v>16.14094</v>
+        <v>16.35791</v>
       </c>
       <c r="E45" t="n">
-        <v>16.3987</v>
+        <v>16.68966</v>
       </c>
       <c r="F45" t="n">
-        <v>22.18731</v>
+        <v>22.04063</v>
       </c>
       <c r="G45" t="n">
-        <v>33.84131</v>
+        <v>35.71548</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.96574</v>
+        <v>16.84081</v>
       </c>
       <c r="D46" t="n">
-        <v>15.99321</v>
+        <v>15.97193</v>
       </c>
       <c r="E46" t="n">
-        <v>16.72191</v>
+        <v>16.46267</v>
       </c>
       <c r="F46" t="n">
-        <v>22.37153</v>
+        <v>21.88711</v>
       </c>
       <c r="G46" t="n">
-        <v>34.93512</v>
+        <v>34.74904</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.7449</v>
+        <v>16.89506</v>
       </c>
       <c r="D47" t="n">
-        <v>16.49313</v>
+        <v>16.32045</v>
       </c>
       <c r="E47" t="n">
-        <v>16.5194</v>
+        <v>16.68629</v>
       </c>
       <c r="F47" t="n">
-        <v>21.99941</v>
+        <v>22.26803</v>
       </c>
       <c r="G47" t="n">
-        <v>34.58257</v>
+        <v>34.56564</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.81253</v>
+        <v>16.90834</v>
       </c>
       <c r="D48" t="n">
-        <v>16.06767</v>
+        <v>16.33233</v>
       </c>
       <c r="E48" t="n">
-        <v>16.61666</v>
+        <v>16.68267</v>
       </c>
       <c r="F48" t="n">
-        <v>22.30463</v>
+        <v>22.12669</v>
       </c>
       <c r="G48" t="n">
-        <v>34.33899</v>
+        <v>34.68341</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.66591</v>
+        <v>16.51646</v>
       </c>
       <c r="D49" t="n">
-        <v>15.94204</v>
+        <v>16.4136</v>
       </c>
       <c r="E49" t="n">
-        <v>16.64184</v>
+        <v>16.50529</v>
       </c>
       <c r="F49" t="n">
-        <v>22.06462</v>
+        <v>21.76459</v>
       </c>
       <c r="G49" t="n">
-        <v>34.99748</v>
+        <v>34.30483</v>
       </c>
     </row>
     <row r="50">
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.98722</v>
+        <v>17.19373</v>
       </c>
       <c r="D50" t="n">
-        <v>15.92659</v>
+        <v>16.38445</v>
       </c>
       <c r="E50" t="n">
-        <v>16.66573</v>
+        <v>16.94551</v>
       </c>
       <c r="F50" t="n">
-        <v>21.66138</v>
+        <v>21.98439</v>
       </c>
       <c r="G50" t="n">
-        <v>35.21613</v>
+        <v>35.19665</v>
       </c>
     </row>
     <row r="51">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.61378</v>
+        <v>0.61034</v>
       </c>
       <c r="D52" t="n">
-        <v>1.14063</v>
+        <v>1.1234</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.60911</v>
+        <v>0.61145</v>
       </c>
       <c r="D53" t="n">
-        <v>1.13772</v>
+        <v>1.11419</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.61978</v>
+        <v>0.6111</v>
       </c>
       <c r="D54" t="n">
-        <v>1.12641</v>
+        <v>1.12882</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.61063</v>
+        <v>0.60898</v>
       </c>
       <c r="D55" t="n">
-        <v>1.12273</v>
+        <v>1.12684</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.61488</v>
+        <v>0.6123499999999999</v>
       </c>
       <c r="D56" t="n">
-        <v>1.09543</v>
+        <v>1.13803</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.61224</v>
+        <v>0.61871</v>
       </c>
       <c r="D57" t="n">
-        <v>1.12414</v>
+        <v>1.13132</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.6097</v>
+        <v>0.61448</v>
       </c>
       <c r="D58" t="n">
-        <v>1.13299</v>
+        <v>1.11699</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.6167</v>
+        <v>0.61912</v>
       </c>
       <c r="D59" t="n">
-        <v>1.11852</v>
+        <v>1.12355</v>
       </c>
     </row>
     <row r="60">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.61609</v>
+        <v>0.62651</v>
       </c>
       <c r="D60" t="n">
-        <v>1.13463</v>
+        <v>1.11074</v>
       </c>
     </row>
     <row r="61">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.61031</v>
+        <v>0.61241</v>
       </c>
       <c r="D62" t="n">
-        <v>1.1242</v>
+        <v>1.12067</v>
       </c>
     </row>
     <row r="63">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.61008</v>
+        <v>0.6129</v>
       </c>
       <c r="D63" t="n">
-        <v>1.12074</v>
+        <v>1.14147</v>
       </c>
     </row>
     <row r="64">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.6096200000000001</v>
+        <v>0.62234</v>
       </c>
       <c r="D64" t="n">
-        <v>1.12694</v>
+        <v>1.14436</v>
       </c>
     </row>
     <row r="65">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.60716</v>
+        <v>0.63174</v>
       </c>
       <c r="D65" t="n">
-        <v>1.1228</v>
+        <v>1.13447</v>
       </c>
     </row>
     <row r="66">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.62646</v>
+        <v>0.62117</v>
       </c>
       <c r="D66" t="n">
-        <v>1.11908</v>
+        <v>1.13981</v>
       </c>
     </row>
     <row r="67">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.61396</v>
+        <v>0.62214</v>
       </c>
       <c r="D67" t="n">
-        <v>1.11945</v>
+        <v>1.12198</v>
       </c>
     </row>
     <row r="68">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.62052</v>
+        <v>0.61578</v>
       </c>
       <c r="D68" t="n">
-        <v>1.13602</v>
+        <v>1.1179</v>
       </c>
     </row>
     <row r="69">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.60924</v>
+        <v>0.61902</v>
       </c>
       <c r="D69" t="n">
-        <v>1.12302</v>
+        <v>1.12101</v>
       </c>
     </row>
     <row r="70">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.6273300000000001</v>
+        <v>0.63458</v>
       </c>
       <c r="D70" t="n">
-        <v>1.13581</v>
+        <v>1.14847</v>
       </c>
     </row>
     <row r="71">
@@ -1920,28 +1920,28 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.75793</v>
+        <v>0.76074</v>
       </c>
       <c r="D72" t="n">
-        <v>0.08221000000000001</v>
+        <v>0.08284999999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>0.61587</v>
+        <v>0.60365</v>
       </c>
       <c r="F72" t="n">
-        <v>0.97057</v>
+        <v>0.9623699999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>0.1113</v>
+        <v>0.11104</v>
       </c>
       <c r="H72" t="n">
-        <v>0.00764</v>
+        <v>0.00779</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09451</v>
+        <v>0.09443</v>
       </c>
       <c r="J72" t="n">
-        <v>0.12591</v>
+        <v>0.12848</v>
       </c>
     </row>
     <row r="73">
@@ -1951,28 +1951,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.74427</v>
+        <v>0.75996</v>
       </c>
       <c r="D73" t="n">
-        <v>0.08118</v>
+        <v>0.08146</v>
       </c>
       <c r="E73" t="n">
-        <v>0.61769</v>
+        <v>0.60898</v>
       </c>
       <c r="F73" t="n">
-        <v>0.97002</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>0.11224</v>
+        <v>0.10985</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00767</v>
+        <v>0.00775</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09411</v>
+        <v>0.09468</v>
       </c>
       <c r="J73" t="n">
-        <v>0.12692</v>
+        <v>0.12707</v>
       </c>
     </row>
     <row r="74">
@@ -1982,28 +1982,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.76871</v>
+        <v>0.75775</v>
       </c>
       <c r="D74" t="n">
-        <v>0.08225</v>
+        <v>0.08209</v>
       </c>
       <c r="E74" t="n">
-        <v>0.62614</v>
+        <v>0.61647</v>
       </c>
       <c r="F74" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.97618</v>
       </c>
       <c r="G74" t="n">
-        <v>0.10992</v>
+        <v>0.11</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00774</v>
+        <v>0.00768</v>
       </c>
       <c r="I74" t="n">
-        <v>0.09314</v>
+        <v>0.09345000000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>0.12619</v>
+        <v>0.12859</v>
       </c>
     </row>
     <row r="75">
@@ -2013,28 +2013,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.7774</v>
+        <v>0.7589900000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>0.08244</v>
+        <v>0.08223</v>
       </c>
       <c r="E75" t="n">
-        <v>0.6085</v>
+        <v>0.61304</v>
       </c>
       <c r="F75" t="n">
-        <v>0.97253</v>
+        <v>0.95783</v>
       </c>
       <c r="G75" t="n">
-        <v>0.11303</v>
+        <v>0.1111</v>
       </c>
       <c r="H75" t="n">
-        <v>0.00775</v>
+        <v>0.00761</v>
       </c>
       <c r="I75" t="n">
-        <v>0.09303</v>
+        <v>0.0958</v>
       </c>
       <c r="J75" t="n">
-        <v>0.12795</v>
+        <v>0.12782</v>
       </c>
     </row>
     <row r="76">
@@ -2044,28 +2044,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.74991</v>
+        <v>0.75363</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08276</v>
+        <v>0.08192000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>0.62037</v>
+        <v>0.62138</v>
       </c>
       <c r="F76" t="n">
-        <v>0.96436</v>
+        <v>0.95318</v>
       </c>
       <c r="G76" t="n">
-        <v>0.11043</v>
+        <v>0.11033</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00763</v>
+        <v>0.00758</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09351</v>
+        <v>0.09467</v>
       </c>
       <c r="J76" t="n">
-        <v>0.12582</v>
+        <v>0.12905</v>
       </c>
     </row>
     <row r="77">
@@ -2075,28 +2075,28 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.74504</v>
+        <v>0.76568</v>
       </c>
       <c r="D77" t="n">
-        <v>0.08128000000000001</v>
+        <v>0.0829</v>
       </c>
       <c r="E77" t="n">
-        <v>0.60851</v>
+        <v>0.6156</v>
       </c>
       <c r="F77" t="n">
-        <v>0.98378</v>
+        <v>1.00986</v>
       </c>
       <c r="G77" t="n">
-        <v>0.10957</v>
+        <v>0.1101</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00766</v>
+        <v>0.00767</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09412</v>
+        <v>0.09564</v>
       </c>
       <c r="J77" t="n">
-        <v>0.12961</v>
+        <v>0.12672</v>
       </c>
     </row>
     <row r="78">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.76362</v>
+        <v>0.76072</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0834</v>
+        <v>0.08187</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6126200000000001</v>
+        <v>0.63188</v>
       </c>
       <c r="F78" t="n">
-        <v>0.95547</v>
+        <v>0.97472</v>
       </c>
       <c r="G78" t="n">
-        <v>0.11116</v>
+        <v>0.10872</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00765</v>
+        <v>0.00774</v>
       </c>
       <c r="I78" t="n">
-        <v>0.09346</v>
+        <v>0.09478</v>
       </c>
       <c r="J78" t="n">
-        <v>0.13</v>
+        <v>0.12438</v>
       </c>
     </row>
     <row r="79">
@@ -2137,28 +2137,28 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.78355</v>
+        <v>0.74352</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0813</v>
+        <v>0.08255</v>
       </c>
       <c r="E79" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.60636</v>
       </c>
       <c r="F79" t="n">
-        <v>0.98556</v>
+        <v>0.96673</v>
       </c>
       <c r="G79" t="n">
-        <v>0.11132</v>
+        <v>0.1059</v>
       </c>
       <c r="H79" t="n">
-        <v>0.00764</v>
+        <v>0.00762</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09472</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J79" t="n">
-        <v>0.12943</v>
+        <v>0.12854</v>
       </c>
     </row>
     <row r="80">
@@ -2168,28 +2168,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.75412</v>
+        <v>0.74884</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08226</v>
+        <v>0.08008</v>
       </c>
       <c r="E80" t="n">
-        <v>0.61624</v>
+        <v>0.62105</v>
       </c>
       <c r="F80" t="n">
-        <v>0.98173</v>
+        <v>0.98536</v>
       </c>
       <c r="G80" t="n">
-        <v>0.11154</v>
+        <v>0.11172</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00767</v>
+        <v>0.00752</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09359000000000001</v>
+        <v>0.09578</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1278</v>
+        <v>0.12997</v>
       </c>
     </row>
   </sheetData>
